--- a/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_INIT.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_INIT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0ACCFE-CC4A-4F0B-B5C6-1AC7A1370C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D31984-60B2-4B69-B144-10C7821016FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4176" yWindow="-17280" windowWidth="15552" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_INIT.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_INIT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D31984-60B2-4B69-B144-10C7821016FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682E881D-BCD9-4894-9ED7-5F44F4DCA755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -651,10 +651,10 @@
     <t>timestep that model progress is displayed [days]</t>
   </si>
   <si>
-    <t>D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\forcing\Forcing_Data\</t>
-  </si>
-  <si>
     <t>TILE_1D</t>
+  </si>
+  <si>
+    <t>..\..\forcing\Forcing_Data\</t>
   </si>
 </sst>
 </file>
@@ -1158,7 +1158,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="28" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B28" s="9">
         <v>1</v>
@@ -1590,10 +1590,10 @@
         <v>33</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
+      <c r="D57" s="17"/>
       <c r="E57" s="14"/>
       <c r="F57" s="14"/>
     </row>

--- a/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_INIT.xlsx
+++ b/CryoGrid/CryoGridCommunity_results/templates/automatic_loops/TILE_LOOP_INIT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Utilisateurs\pozsgayv\Documents\CryoGrid_VP_Workflow\CryoGrid\CryoGridCommunity_results\templates\automatic_loops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6443D41A-308B-499E-9451-F6C5EBE86DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4963C81E-3C41-49E5-ADB2-704E91762976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="211">
   <si>
     <t>-------------------</t>
   </si>
@@ -639,9 +639,6 @@
     <t>OUT_do_nothing</t>
   </si>
   <si>
-    <t>loop1</t>
-  </si>
-  <si>
     <t>display_timestep</t>
   </si>
   <si>
@@ -649,6 +646,27 @@
   </si>
   <si>
     <t>TILE_1D</t>
+  </si>
+  <si>
+    <t>use_save_date</t>
+  </si>
+  <si>
+    <t>if 0/false (default), normal behaviour with file being overwritten every save_timestep [days]; if 1/true, then a new file with tile index and spinup index is created to prevent overwriting (uses save_date and save_interval below)</t>
+  </si>
+  <si>
+    <t>save_date</t>
+  </si>
+  <si>
+    <t>01.09.</t>
+  </si>
+  <si>
+    <t>date (dd.mm.) when output file is written</t>
+  </si>
+  <si>
+    <t>save_interval</t>
+  </si>
+  <si>
+    <t>interval of output files [years]</t>
   </si>
 </sst>
 </file>
@@ -1064,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J232"/>
+  <dimension ref="A1:J235"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" outlineLevelRow="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.54296875" style="9" customWidth="1"/>
@@ -1127,7 +1145,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>24</v>
@@ -1265,7 +1283,7 @@
     </row>
     <row r="28" spans="1:4" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B28" s="9">
         <v>1</v>
@@ -1701,7 +1719,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B78" s="9">
         <v>5</v>
@@ -1710,7 +1728,7 @@
         <v>5</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
@@ -1718,12 +1736,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" s="9" t="s">
         <v>40</v>
       </c>
@@ -1731,7 +1749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" s="9" t="s">
         <v>197</v>
       </c>
@@ -1739,1378 +1757,1410 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A86" s="9" t="s">
+    <row r="86" spans="1:4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>198</v>
       </c>
-      <c r="B86" s="9">
-        <v>5</v>
-      </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A87" s="9" t="s">
+    <row r="87" spans="1:4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>43</v>
       </c>
-      <c r="B87" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="D87" s="4"/>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A88" s="9" t="s">
+    </row>
+    <row r="88" spans="1:4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>204</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>206</v>
+      </c>
+      <c r="B89" t="s">
+        <v>207</v>
+      </c>
+      <c r="C89" t="s">
+        <v>207</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>209</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A91" s="9" t="s">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A92" s="9" t="s">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B95" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A93" s="9" t="s">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B93" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A95" s="9" t="s">
+      <c r="B96" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B98" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C95" s="9" t="s">
+      <c r="C98" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D95" s="9" t="s">
+      <c r="D98" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E95" s="9" t="s">
+      <c r="E98" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F95" s="9" t="s">
+      <c r="F98" s="9" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C96" s="9">
-        <v>0</v>
-      </c>
-      <c r="D96" s="15">
-        <v>0.05</v>
-      </c>
-      <c r="E96" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C97" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="D97" s="15">
-        <v>0.05</v>
-      </c>
-      <c r="E97" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C98" s="9">
-        <v>3</v>
-      </c>
-      <c r="D98" s="15">
-        <v>0.1</v>
-      </c>
-      <c r="E98" s="9">
-        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C99" s="9">
-        <v>10</v>
-      </c>
-      <c r="D99" s="9">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="D99" s="15">
+        <v>0.05</v>
       </c>
       <c r="E99" s="9">
-        <v>50</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C100" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D100" s="15">
+        <v>0.05</v>
+      </c>
+      <c r="E100" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C101" s="9">
+        <v>3</v>
+      </c>
+      <c r="D101" s="15">
+        <v>0.1</v>
+      </c>
+      <c r="E101" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C102" s="9">
+        <v>10</v>
+      </c>
+      <c r="D102" s="9">
+        <v>1</v>
+      </c>
+      <c r="E102" s="9">
         <v>50</v>
       </c>
-      <c r="D100" s="15">
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C103" s="9">
+        <v>50</v>
+      </c>
+      <c r="D103" s="15">
         <v>5</v>
       </c>
-      <c r="E100" s="9">
+      <c r="E103" s="9">
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B101" s="9" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B104" s="9" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" s="9" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="9" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B106" s="9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B107" s="9">
-        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B110" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B109" s="9" t="s">
+      <c r="B112" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C109" s="9" t="s">
+      <c r="C112" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D109" s="9" t="s">
+      <c r="D112" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E109" s="9" t="s">
+      <c r="E112" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F109" s="4" t="s">
+      <c r="F112" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B110" s="9">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B113" s="9">
         <v>0</v>
       </c>
-      <c r="C110" s="9" t="s">
+      <c r="C113" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D110" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B111" s="9">
+      <c r="D113" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B114" s="9">
         <v>5</v>
       </c>
-      <c r="C111" s="9" t="s">
+      <c r="C114" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D111" s="9">
-        <v>1</v>
-      </c>
-      <c r="F111" s="4" t="s">
+      <c r="D114" s="9">
+        <v>1</v>
+      </c>
+      <c r="F114" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="B112" s="9" t="s">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B115" s="9" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A113" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A114" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B114" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A115" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C115" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D115" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" s="9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C116" s="9" t="s">
-        <v>24</v>
+        <v>145</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" s="9" t="s">
-        <v>6</v>
+        <v>58</v>
+      </c>
+      <c r="B117" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A118" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A119" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A123" s="9" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A121" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B121" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D121" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A122" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B122" s="9">
-        <v>1</v>
-      </c>
-      <c r="D122" s="16" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D124" s="16" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A125" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B125" s="9">
+        <v>1</v>
+      </c>
+      <c r="D125" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A127" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B124" s="9" t="s">
+      <c r="B127" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C124" s="9" t="s">
+      <c r="C127" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D124" s="9" t="s">
+      <c r="D127" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E124" s="9" t="s">
+      <c r="E127" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F124" s="9" t="s">
+      <c r="F127" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="G124" s="9" t="s">
+      <c r="G127" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H124" s="9" t="s">
+      <c r="H127" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="I124" s="9" t="s">
+      <c r="I127" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="J124" s="4" t="s">
+      <c r="J127" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B125" s="9">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B128" s="9">
         <v>0</v>
       </c>
-      <c r="C125" s="9">
+      <c r="C128" s="9">
         <v>0.4</v>
       </c>
-      <c r="D125" s="9">
+      <c r="D128" s="9">
         <v>0.6</v>
       </c>
-      <c r="E125" s="9">
+      <c r="E128" s="9">
         <v>0</v>
       </c>
-      <c r="F125" s="9">
+      <c r="F128" s="9">
         <v>2</v>
       </c>
-      <c r="G125" s="9">
+      <c r="G128" s="9">
         <v>0.2</v>
       </c>
-      <c r="H125" s="8">
+      <c r="H128" s="8">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B126" s="9">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B129" s="9">
         <v>0.1</v>
       </c>
-      <c r="C126" s="9">
+      <c r="C129" s="9">
         <v>0.4</v>
       </c>
-      <c r="D126" s="9">
+      <c r="D129" s="9">
         <v>0.6</v>
       </c>
-      <c r="E126" s="9">
+      <c r="E129" s="9">
         <v>0</v>
       </c>
-      <c r="F126" s="9">
+      <c r="F129" s="9">
         <v>2</v>
       </c>
-      <c r="G126" s="9">
+      <c r="G129" s="9">
         <v>0.2</v>
       </c>
-      <c r="H126" s="8">
+      <c r="H129" s="8">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B127" s="9">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B130" s="9">
         <v>5</v>
       </c>
-      <c r="C127" s="9">
+      <c r="C130" s="9">
         <v>0.03</v>
       </c>
-      <c r="D127" s="9">
+      <c r="D130" s="9">
         <v>0.97</v>
       </c>
-      <c r="E127" s="9">
+      <c r="E130" s="9">
         <v>0</v>
       </c>
-      <c r="F127" s="9">
-        <v>1</v>
-      </c>
-      <c r="G127" s="9">
+      <c r="F130" s="9">
+        <v>1</v>
+      </c>
+      <c r="G130" s="9">
         <v>0.03</v>
       </c>
-      <c r="H127" s="8">
+      <c r="H130" s="8">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B128" s="9" t="s">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B131" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G128" s="16" t="s">
+      <c r="G131" s="16" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A129" s="9" t="s">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A132" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G129" s="16" t="s">
+      <c r="G132" s="16" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="G130" s="16" t="s">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G133" s="16" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="131" spans="1:7" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A132" s="10" t="s">
+    <row r="134" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A135" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B132" s="10"/>
-      <c r="C132" s="10"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A133" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B133" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C133" s="10"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A134" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B134" s="10">
-        <v>1</v>
-      </c>
-      <c r="C134" s="10"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A135" s="10"/>
       <c r="B135" s="10"/>
       <c r="C135" s="10"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B136" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C136" s="10"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A137" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B137" s="10">
+        <v>1</v>
+      </c>
+      <c r="C137" s="10"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A138" s="10"/>
+      <c r="B138" s="10"/>
+      <c r="C138" s="10"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A139" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B136" s="10" t="s">
+      <c r="B139" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C136" s="6" t="s">
+      <c r="C139" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D136" s="9" t="s">
+      <c r="D139" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A137" s="10"/>
-      <c r="B137" s="10">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A140" s="10"/>
+      <c r="B140" s="10">
         <v>0</v>
       </c>
-      <c r="C137" s="6">
+      <c r="C140" s="6">
         <v>-2</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A138" s="10"/>
-      <c r="B138" s="6">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A141" s="10"/>
+      <c r="B141" s="6">
         <v>100</v>
       </c>
-      <c r="C138" s="6">
+      <c r="C141" s="6">
         <v>-2</v>
       </c>
-      <c r="D138" s="9" t="s">
+      <c r="D141" s="9" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A139" s="10"/>
-      <c r="B139" s="10" t="s">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A142" s="10"/>
+      <c r="B142" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C139" s="17"/>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A140" s="10" t="s">
+      <c r="C142" s="17"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A143" s="10" t="s">
         <v>6</v>
-      </c>
-      <c r="B140" s="10"/>
-      <c r="C140" s="10"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A141" s="10"/>
-      <c r="B141" s="10"/>
-      <c r="C141" s="10"/>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A142" s="10"/>
-      <c r="B142" s="10"/>
-      <c r="C142" s="10"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A143" s="10" t="s">
-        <v>0</v>
       </c>
       <c r="B143" s="10"/>
       <c r="C143" s="10"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A144" s="10" t="s">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A144" s="10"/>
+      <c r="B144" s="10"/>
+      <c r="C144" s="10"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A145" s="10"/>
+      <c r="B145" s="10"/>
+      <c r="C145" s="10"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A146" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B146" s="10"/>
+      <c r="C146" s="10"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A147" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B144" s="10" t="s">
+      <c r="B147" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C144" s="10"/>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A145" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B145" s="10">
-        <v>1</v>
-      </c>
-      <c r="C145" s="10"/>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A146" s="10"/>
-      <c r="B146" s="10"/>
-      <c r="C146" s="10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A147" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B147" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="C147" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="C147" s="10"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" s="10" t="s">
-        <v>71</v>
+        <v>146</v>
       </c>
       <c r="B148" s="10">
-        <v>0.99</v>
-      </c>
-      <c r="C148" s="10">
-        <v>0.99</v>
-      </c>
-      <c r="D148" s="4" t="s">
-        <v>72</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C148" s="10"/>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="B149" s="10">
-        <v>0.27</v>
-      </c>
-      <c r="C149" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="D149" s="4" t="s">
-        <v>74</v>
+      <c r="A149" s="10"/>
+      <c r="B149" s="10"/>
+      <c r="C149" s="10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B150" s="10">
-        <v>0.1</v>
+      <c r="A150" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B150" s="6">
+        <v>0.25</v>
       </c>
       <c r="C150" s="10">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>189</v>
+        <v>70</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" s="10" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="B151" s="10">
-        <v>0.1</v>
+        <v>0.99</v>
       </c>
       <c r="C151" s="10">
-        <v>0.1</v>
+        <v>0.99</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" s="10" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="B152" s="10">
-        <v>0.5</v>
+        <v>0.27</v>
       </c>
       <c r="C152" s="10">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>191</v>
+        <v>74</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" s="10" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="B153" s="10">
-        <v>1.0000000000000001E-5</v>
+        <v>0.1</v>
       </c>
       <c r="C153" s="10">
-        <v>1.0000000000000001E-5</v>
+        <v>0.1</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="B154" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="C154" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A155" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B155" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="C155" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A156" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B156" s="10">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="C156" s="10">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A157" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B154" s="10" t="s">
+      <c r="B157" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C154" s="10" t="s">
+      <c r="C157" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D154" s="4" t="s">
+      <c r="D157" s="4" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A155" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B155" s="9">
-        <v>3600</v>
-      </c>
-      <c r="C155" s="9">
-        <v>3600</v>
-      </c>
-      <c r="D155" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A156" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B156" s="9">
-        <v>50000</v>
-      </c>
-      <c r="C156" s="9">
-        <v>50000</v>
-      </c>
-      <c r="D156" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A157" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="B157" s="9">
-        <v>1000</v>
-      </c>
-      <c r="C157" s="9">
-        <v>1000</v>
-      </c>
-      <c r="D157" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" s="9" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="B158" s="9">
-        <v>1000</v>
+        <v>3600</v>
       </c>
       <c r="C158" s="9">
-        <v>1000</v>
+        <v>3600</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>140</v>
+        <v>80</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" s="9" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="B159" s="9">
-        <v>-40</v>
+        <v>50000</v>
       </c>
       <c r="C159" s="9">
-        <v>-50</v>
+        <v>50000</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" s="9" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B160" s="9">
-        <v>0.05</v>
+        <v>1000</v>
       </c>
       <c r="C160" s="9">
-        <v>0.05</v>
+        <v>1000</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" s="9" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B161" s="9">
-        <v>0.97</v>
+        <v>1000</v>
       </c>
       <c r="C161" s="9">
-        <v>0.97</v>
+        <v>1000</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" s="9" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B162" s="9">
-        <v>0.03</v>
+        <v>-40</v>
       </c>
       <c r="C162" s="9">
-        <v>0.03</v>
+        <v>-50</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" s="9" t="s">
-        <v>6</v>
+        <v>131</v>
+      </c>
+      <c r="B163" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="C163" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A164" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B164" s="9">
+        <v>0.97</v>
+      </c>
+      <c r="C164" s="9">
+        <v>0.97</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A165" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B165" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="C165" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A169" s="9" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A167" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B167" s="9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A168" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="B168" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C169" s="9" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B170" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="C170" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="D170" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="B170" s="9" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" s="9" t="s">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="B171" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="C171" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="D171" s="4" t="s">
-        <v>72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A172" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B172" s="10">
-        <v>0.27</v>
-      </c>
-      <c r="C172" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="D172" s="4" t="s">
-        <v>74</v>
+      <c r="C172" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" s="9" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="B173" s="9">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="C173" s="9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>193</v>
+        <v>70</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B174" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C174" s="9" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="B174" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="C174" s="9">
+        <v>0.99</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B175" s="9">
-        <v>3600</v>
+        <v>73</v>
+      </c>
+      <c r="B175" s="10">
+        <v>0.27</v>
       </c>
       <c r="C175" s="9">
-        <v>3600</v>
+        <v>0.01</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" s="9" t="s">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="B176" s="9">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="C176" s="9">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" s="9" t="s">
-        <v>6</v>
+        <v>76</v>
+      </c>
+      <c r="B177" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C177" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A178" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B178" s="9">
+        <v>3600</v>
+      </c>
+      <c r="C178" s="9">
+        <v>3600</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A179" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B179" s="9">
+        <v>50000</v>
+      </c>
+      <c r="C179" s="9">
+        <v>50000</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A183" s="9" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A181" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B181" s="9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A182" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="B182" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C183" s="9" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="B184" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="C184" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="D184" s="4" t="s">
-        <v>72</v>
+        <v>83</v>
+      </c>
+      <c r="B184" s="9" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A185" s="9" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="B185" s="9">
-        <v>1E-3</v>
-      </c>
-      <c r="C185" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="D185" s="4" t="s">
-        <v>74</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A186" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B186" s="9">
-        <v>0.71</v>
-      </c>
-      <c r="C186" s="9">
-        <v>0.71</v>
-      </c>
-      <c r="D186" s="4" t="s">
-        <v>85</v>
+      <c r="C186" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A187" s="9" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B187" s="9">
-        <v>0.21</v>
+        <v>0.99</v>
       </c>
       <c r="C187" s="9">
-        <v>0.21</v>
+        <v>0.99</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" s="9" t="s">
-        <v>88</v>
+        <v>73</v>
+      </c>
+      <c r="B188" s="9">
+        <v>1E-3</v>
+      </c>
+      <c r="C188" s="9">
+        <v>0.01</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" s="9" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B189" s="9">
-        <v>0.05</v>
+        <v>0.71</v>
       </c>
       <c r="C189" s="9">
-        <v>0.05</v>
+        <v>0.71</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" s="9" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B190" s="9">
-        <v>1E-4</v>
+        <v>0.21</v>
       </c>
       <c r="C190" s="9">
-        <v>1E-4</v>
+        <v>0.21</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B191" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="C191" s="9">
-        <v>0.02</v>
+        <v>88</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" s="9" t="s">
-        <v>194</v>
+        <v>66</v>
       </c>
       <c r="B192" s="9">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C192" s="9">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>195</v>
+        <v>90</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B193" s="9">
+        <v>1E-4</v>
+      </c>
+      <c r="C193" s="9">
+        <v>1E-4</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A194" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B194" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="C194" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A195" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B195" s="9">
+        <v>0</v>
+      </c>
+      <c r="C195" s="9">
+        <v>0</v>
+      </c>
+      <c r="D195" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A196" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="B193" s="9">
+      <c r="B196" s="9">
         <f>48/3</f>
         <v>16</v>
       </c>
-      <c r="C193" s="9">
+      <c r="C196" s="9">
         <v>48</v>
       </c>
-      <c r="D193" s="4" t="s">
+      <c r="D196" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A194" s="9" t="s">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A197" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B194" s="9">
+      <c r="B197" s="9">
         <v>600</v>
       </c>
-      <c r="C194" s="9">
+      <c r="C197" s="9">
         <v>350</v>
       </c>
-      <c r="D194" s="4" t="s">
+      <c r="D197" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A195" s="9" t="s">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A198" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B195" s="9">
+      <c r="B198" s="9">
         <v>52</v>
       </c>
-      <c r="C195" s="9">
+      <c r="C198" s="9">
         <v>26</v>
       </c>
-      <c r="D195" s="4" t="s">
+      <c r="D198" s="4" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A196" s="9" t="s">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A199" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B196" s="9">
+      <c r="B199" s="9">
         <f>0.06/60</f>
         <v>1E-3</v>
       </c>
-      <c r="D196" s="4" t="s">
+      <c r="D199" s="4" t="s">
         <v>101</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A197" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B197" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C197" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="D197" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A198" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B198" s="9">
-        <v>3600</v>
-      </c>
-      <c r="C198" s="9">
-        <v>3600</v>
-      </c>
-      <c r="D198" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A199" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="B199" s="9">
-        <v>50000</v>
-      </c>
-      <c r="C199" s="9">
-        <v>50000</v>
-      </c>
-      <c r="D199" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D200" s="4"/>
+        <v>76</v>
+      </c>
+      <c r="B200" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C200" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="D200" s="4" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" s="9" t="s">
-        <v>6</v>
+        <v>79</v>
+      </c>
+      <c r="B201" s="9">
+        <v>3600</v>
+      </c>
+      <c r="C201" s="9">
+        <v>3600</v>
+      </c>
+      <c r="D201" s="4" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D202" s="4"/>
+      <c r="A202" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B202" s="9">
+        <v>50000</v>
+      </c>
+      <c r="C202" s="9">
+        <v>50000</v>
+      </c>
+      <c r="D202" s="4" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A203" s="9" t="s">
+        <v>122</v>
+      </c>
       <c r="D203" s="4"/>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D205" s="4"/>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D206" s="4"/>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A207" s="9" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A205" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="B205" s="9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A206" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B206" s="9">
-        <v>1</v>
-      </c>
-      <c r="D206" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C207" s="9" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="B208" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="C208" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="D208" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
+      </c>
+      <c r="B208" s="9" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" s="9" t="s">
-        <v>6</v>
+        <v>27</v>
+      </c>
+      <c r="B209" s="9">
+        <v>1</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D210" s="4"/>
+      <c r="C210" s="9" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D211" s="4"/>
+      <c r="A211" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B211" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="C211" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="D211" s="4" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D213" s="4"/>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D214" s="4"/>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A215" s="9" t="s">
         <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A213" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B213" s="9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A214" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B214" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C215" s="9" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="B216" s="9">
-        <v>20</v>
-      </c>
-      <c r="C216" s="9">
-        <v>10000</v>
-      </c>
-      <c r="D216" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
+      </c>
+      <c r="B216" s="9" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B217" s="9">
-        <v>0</v>
-      </c>
-      <c r="C217" s="9">
-        <v>0</v>
-      </c>
-      <c r="D217" s="4" t="s">
-        <v>111</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A218" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B218" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="C218" s="9">
-        <v>0.03</v>
-      </c>
-      <c r="D218" s="4" t="s">
-        <v>113</v>
+      <c r="C218" s="9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" s="9" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B219" s="9">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C219" s="9">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" s="9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B220" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C220" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B221" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="C221" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="D221" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A222" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B222" s="9">
+        <v>5</v>
+      </c>
+      <c r="C222" s="9">
+        <v>1</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A223" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B223" s="9">
+        <v>1</v>
+      </c>
+      <c r="C223" s="9">
+        <v>1</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A224" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D222" s="4"/>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="D223" s="4"/>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A224" s="18" t="s">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D225" s="4"/>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D226" s="4"/>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A227" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="D224" s="4"/>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A225" s="9" t="s">
+      <c r="D227" s="4"/>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A228" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="B225" s="9" t="s">
+      <c r="B228" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D225" s="4"/>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A226" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="B226" s="9">
-        <v>1</v>
-      </c>
-      <c r="D226" s="4"/>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A227" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B227" s="2"/>
-      <c r="D227" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A228" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B228" s="2"/>
       <c r="D228" s="4"/>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A229" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="B229" s="2">
-        <v>0.03</v>
+        <v>147</v>
+      </c>
+      <c r="B229" s="9">
+        <v>1</v>
       </c>
       <c r="D229" s="4"/>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A230" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B230" s="2">
-        <v>50</v>
-      </c>
-      <c r="D230" s="4"/>
+      <c r="A230" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B230" s="2"/>
+      <c r="D230" s="4" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B231" s="2">
-        <v>1</v>
-      </c>
-      <c r="D231" s="4" t="s">
-        <v>157</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="B231" s="2"/>
+      <c r="D231" s="4"/>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A232" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B232" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="D232" s="4"/>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A233" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B233" s="2">
+        <v>50</v>
+      </c>
+      <c r="D233" s="4"/>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A234" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B234" s="2">
+        <v>1</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A235" s="9" t="s">
         <v>6</v>
       </c>
     </row>
